--- a/evaluation/config_periods.xlsx
+++ b/evaluation/config_periods.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\6. calibration.py\evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000DD680-8DC3-4908-97F9-66D26859AC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57631634-1FF3-4EED-89A2-BA8301B64A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,10 +16,19 @@
     <sheet name="simulation_periods" sheetId="1" r:id="rId1"/>
     <sheet name="flow_periods" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -98,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="24">
   <si>
     <t>catchment</t>
   </si>
@@ -155,6 +164,21 @@
   </si>
   <si>
     <t>flow_period_type</t>
+  </si>
+  <si>
+    <t>Greenvale</t>
+  </si>
+  <si>
+    <t>2023_2025</t>
+  </si>
+  <si>
+    <t>6.2022</t>
+  </si>
+  <si>
+    <t>6.2018</t>
+  </si>
+  <si>
+    <t>2019_2021</t>
   </si>
 </sst>
 </file>
@@ -507,13 +531,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -583,6 +607,52 @@
       </c>
       <c r="G3" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1">
+        <v>43466</v>
+      </c>
+      <c r="C4" s="1">
+        <v>44561.958333333336</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="1">
+        <v>44927</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46022.958333333336</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -593,7 +663,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73BA915D-2D9F-4136-846C-CF5EA63AD913}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
@@ -980,6 +1050,1546 @@
         <v>19455</v>
       </c>
     </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>4161</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>4654</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>7131</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>13195</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>14322</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>16224</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>20153</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>21646</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2</v>
+      </c>
+      <c r="D39">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41">
+        <v>4161</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42">
+        <v>4654</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43">
+        <v>7131</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44">
+        <v>8636</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45">
+        <v>8861</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46">
+        <v>9955</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47">
+        <v>10280</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2</v>
+      </c>
+      <c r="D48">
+        <v>10563</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" t="s">
+        <v>23</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49">
+        <v>11988</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2</v>
+      </c>
+      <c r="D50">
+        <v>12536</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2</v>
+      </c>
+      <c r="D51">
+        <v>13195</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B52" t="s">
+        <v>23</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52">
+        <v>14322</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>19</v>
+      </c>
+      <c r="B53" t="s">
+        <v>23</v>
+      </c>
+      <c r="C53" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53">
+        <v>15761</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>19</v>
+      </c>
+      <c r="B54" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54">
+        <v>16224</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B55" t="s">
+        <v>23</v>
+      </c>
+      <c r="C55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55">
+        <v>16740</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B56" t="s">
+        <v>23</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2</v>
+      </c>
+      <c r="D56">
+        <v>16912</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B57" t="s">
+        <v>23</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2</v>
+      </c>
+      <c r="D57">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>19</v>
+      </c>
+      <c r="B58" t="s">
+        <v>23</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2</v>
+      </c>
+      <c r="D58">
+        <v>17228</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>19</v>
+      </c>
+      <c r="B59" t="s">
+        <v>23</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2</v>
+      </c>
+      <c r="D59">
+        <v>17471</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>19</v>
+      </c>
+      <c r="B60" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" t="s">
+        <v>2</v>
+      </c>
+      <c r="D60">
+        <v>17921</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>19</v>
+      </c>
+      <c r="B61" t="s">
+        <v>23</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2</v>
+      </c>
+      <c r="D61">
+        <v>18077</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2</v>
+      </c>
+      <c r="D62">
+        <v>18170</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63" t="s">
+        <v>23</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2</v>
+      </c>
+      <c r="D63">
+        <v>18295</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>19</v>
+      </c>
+      <c r="B64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" t="s">
+        <v>2</v>
+      </c>
+      <c r="D64">
+        <v>18392</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2</v>
+      </c>
+      <c r="D65">
+        <v>18535</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>19</v>
+      </c>
+      <c r="B66" t="s">
+        <v>23</v>
+      </c>
+      <c r="C66" t="s">
+        <v>2</v>
+      </c>
+      <c r="D66">
+        <v>18565</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C67" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67">
+        <v>18603</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>19</v>
+      </c>
+      <c r="B68" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68" t="s">
+        <v>2</v>
+      </c>
+      <c r="D68">
+        <v>18644</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>19</v>
+      </c>
+      <c r="B69" t="s">
+        <v>23</v>
+      </c>
+      <c r="C69" t="s">
+        <v>2</v>
+      </c>
+      <c r="D69">
+        <v>20153</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>19</v>
+      </c>
+      <c r="B70" t="s">
+        <v>23</v>
+      </c>
+      <c r="C70" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70">
+        <v>21238</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>19</v>
+      </c>
+      <c r="B71" t="s">
+        <v>23</v>
+      </c>
+      <c r="C71" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71">
+        <v>21646</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72">
+        <v>22673</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>19</v>
+      </c>
+      <c r="B73" t="s">
+        <v>23</v>
+      </c>
+      <c r="C73" t="s">
+        <v>2</v>
+      </c>
+      <c r="D73">
+        <v>23857</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>19</v>
+      </c>
+      <c r="B74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C74" t="s">
+        <v>2</v>
+      </c>
+      <c r="D74">
+        <v>24047</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>19</v>
+      </c>
+      <c r="B75" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75" t="s">
+        <v>2</v>
+      </c>
+      <c r="D75">
+        <v>24582</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>19</v>
+      </c>
+      <c r="B76" t="s">
+        <v>23</v>
+      </c>
+      <c r="C76" t="s">
+        <v>2</v>
+      </c>
+      <c r="D76">
+        <v>24971</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>19</v>
+      </c>
+      <c r="B77" t="s">
+        <v>23</v>
+      </c>
+      <c r="C77" t="s">
+        <v>2</v>
+      </c>
+      <c r="D77">
+        <v>25256</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>19</v>
+      </c>
+      <c r="B78" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78" t="s">
+        <v>2</v>
+      </c>
+      <c r="D78">
+        <v>25381</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>19</v>
+      </c>
+      <c r="B79" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79" t="s">
+        <v>2</v>
+      </c>
+      <c r="D79">
+        <v>25500</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>19</v>
+      </c>
+      <c r="B80" t="s">
+        <v>23</v>
+      </c>
+      <c r="C80" t="s">
+        <v>2</v>
+      </c>
+      <c r="D80">
+        <v>25794</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" t="s">
+        <v>23</v>
+      </c>
+      <c r="C81" t="s">
+        <v>2</v>
+      </c>
+      <c r="D81">
+        <v>25917</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>19</v>
+      </c>
+      <c r="B82" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82" t="s">
+        <v>2</v>
+      </c>
+      <c r="D82">
+        <v>25964</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>19</v>
+      </c>
+      <c r="B83" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" t="s">
+        <v>2</v>
+      </c>
+      <c r="D83">
+        <v>26068</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>19</v>
+      </c>
+      <c r="B84" t="s">
+        <v>23</v>
+      </c>
+      <c r="C84" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84">
+        <v>26157</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>19</v>
+      </c>
+      <c r="B85" t="s">
+        <v>20</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>19</v>
+      </c>
+      <c r="B86" t="s">
+        <v>20</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1</v>
+      </c>
+      <c r="D86">
+        <v>3811</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>19</v>
+      </c>
+      <c r="B87" t="s">
+        <v>20</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1</v>
+      </c>
+      <c r="D87">
+        <v>4940</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>19</v>
+      </c>
+      <c r="B88" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1</v>
+      </c>
+      <c r="D88">
+        <v>7482</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>19</v>
+      </c>
+      <c r="B89" t="s">
+        <v>20</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1</v>
+      </c>
+      <c r="D89">
+        <v>14626</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>19</v>
+      </c>
+      <c r="B90" t="s">
+        <v>20</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1</v>
+      </c>
+      <c r="D90">
+        <v>16550</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>19</v>
+      </c>
+      <c r="B91" t="s">
+        <v>20</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1</v>
+      </c>
+      <c r="D91">
+        <v>18723</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>19</v>
+      </c>
+      <c r="B92" t="s">
+        <v>20</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1</v>
+      </c>
+      <c r="D92">
+        <v>20524</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>19</v>
+      </c>
+      <c r="B93" t="s">
+        <v>20</v>
+      </c>
+      <c r="C93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B94" t="s">
+        <v>20</v>
+      </c>
+      <c r="C94" t="s">
+        <v>2</v>
+      </c>
+      <c r="D94">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>19</v>
+      </c>
+      <c r="B95" t="s">
+        <v>20</v>
+      </c>
+      <c r="C95" t="s">
+        <v>2</v>
+      </c>
+      <c r="D95">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>19</v>
+      </c>
+      <c r="B96" t="s">
+        <v>20</v>
+      </c>
+      <c r="C96" t="s">
+        <v>2</v>
+      </c>
+      <c r="D96">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>19</v>
+      </c>
+      <c r="B97" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97" t="s">
+        <v>2</v>
+      </c>
+      <c r="D97">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>19</v>
+      </c>
+      <c r="B98" t="s">
+        <v>20</v>
+      </c>
+      <c r="C98" t="s">
+        <v>2</v>
+      </c>
+      <c r="D98">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>19</v>
+      </c>
+      <c r="B99" t="s">
+        <v>20</v>
+      </c>
+      <c r="C99" t="s">
+        <v>2</v>
+      </c>
+      <c r="D99">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>19</v>
+      </c>
+      <c r="B100" t="s">
+        <v>20</v>
+      </c>
+      <c r="C100" t="s">
+        <v>2</v>
+      </c>
+      <c r="D100">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>19</v>
+      </c>
+      <c r="B101" t="s">
+        <v>20</v>
+      </c>
+      <c r="C101" t="s">
+        <v>2</v>
+      </c>
+      <c r="D101">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>19</v>
+      </c>
+      <c r="B102" t="s">
+        <v>20</v>
+      </c>
+      <c r="C102" t="s">
+        <v>2</v>
+      </c>
+      <c r="D102">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>19</v>
+      </c>
+      <c r="B103" t="s">
+        <v>20</v>
+      </c>
+      <c r="C103" t="s">
+        <v>2</v>
+      </c>
+      <c r="D103">
+        <v>3238</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>19</v>
+      </c>
+      <c r="B104" t="s">
+        <v>20</v>
+      </c>
+      <c r="C104" t="s">
+        <v>2</v>
+      </c>
+      <c r="D104">
+        <v>3811</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>19</v>
+      </c>
+      <c r="B105" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105" t="s">
+        <v>2</v>
+      </c>
+      <c r="D105">
+        <v>4940</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>19</v>
+      </c>
+      <c r="B106" t="s">
+        <v>20</v>
+      </c>
+      <c r="C106" t="s">
+        <v>2</v>
+      </c>
+      <c r="D106">
+        <v>5985</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>19</v>
+      </c>
+      <c r="B107" t="s">
+        <v>20</v>
+      </c>
+      <c r="C107" t="s">
+        <v>2</v>
+      </c>
+      <c r="D107">
+        <v>6595</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>19</v>
+      </c>
+      <c r="B108" t="s">
+        <v>20</v>
+      </c>
+      <c r="C108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D108">
+        <v>6799</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>19</v>
+      </c>
+      <c r="B109" t="s">
+        <v>20</v>
+      </c>
+      <c r="C109" t="s">
+        <v>2</v>
+      </c>
+      <c r="D109">
+        <v>7482</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>19</v>
+      </c>
+      <c r="B110" t="s">
+        <v>20</v>
+      </c>
+      <c r="C110" t="s">
+        <v>2</v>
+      </c>
+      <c r="D110">
+        <v>7854</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>19</v>
+      </c>
+      <c r="B111" t="s">
+        <v>20</v>
+      </c>
+      <c r="C111" t="s">
+        <v>2</v>
+      </c>
+      <c r="D111">
+        <v>7965</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>19</v>
+      </c>
+      <c r="B112" t="s">
+        <v>20</v>
+      </c>
+      <c r="C112" t="s">
+        <v>2</v>
+      </c>
+      <c r="D112">
+        <v>8093</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>19</v>
+      </c>
+      <c r="B113" t="s">
+        <v>20</v>
+      </c>
+      <c r="C113" t="s">
+        <v>2</v>
+      </c>
+      <c r="D113">
+        <v>8331</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>19</v>
+      </c>
+      <c r="B114" t="s">
+        <v>20</v>
+      </c>
+      <c r="C114" t="s">
+        <v>2</v>
+      </c>
+      <c r="D114">
+        <v>9262</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>19</v>
+      </c>
+      <c r="B115" t="s">
+        <v>20</v>
+      </c>
+      <c r="C115" t="s">
+        <v>2</v>
+      </c>
+      <c r="D115">
+        <v>9715</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>19</v>
+      </c>
+      <c r="B116" t="s">
+        <v>20</v>
+      </c>
+      <c r="C116" t="s">
+        <v>2</v>
+      </c>
+      <c r="D116">
+        <v>14626</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>19</v>
+      </c>
+      <c r="B117" t="s">
+        <v>20</v>
+      </c>
+      <c r="C117" t="s">
+        <v>2</v>
+      </c>
+      <c r="D117">
+        <v>16550</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>19</v>
+      </c>
+      <c r="B118" t="s">
+        <v>20</v>
+      </c>
+      <c r="C118" t="s">
+        <v>2</v>
+      </c>
+      <c r="D118">
+        <v>16798</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>19</v>
+      </c>
+      <c r="B119" t="s">
+        <v>20</v>
+      </c>
+      <c r="C119" t="s">
+        <v>2</v>
+      </c>
+      <c r="D119">
+        <v>17940</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>19</v>
+      </c>
+      <c r="B120" t="s">
+        <v>20</v>
+      </c>
+      <c r="C120" t="s">
+        <v>2</v>
+      </c>
+      <c r="D120">
+        <v>18087</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>19</v>
+      </c>
+      <c r="B121" t="s">
+        <v>20</v>
+      </c>
+      <c r="C121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D121">
+        <v>18723</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>19</v>
+      </c>
+      <c r="B122" t="s">
+        <v>20</v>
+      </c>
+      <c r="C122" t="s">
+        <v>2</v>
+      </c>
+      <c r="D122">
+        <v>18852</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>19</v>
+      </c>
+      <c r="B123" t="s">
+        <v>20</v>
+      </c>
+      <c r="C123" t="s">
+        <v>2</v>
+      </c>
+      <c r="D123">
+        <v>19153</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>19</v>
+      </c>
+      <c r="B124" t="s">
+        <v>20</v>
+      </c>
+      <c r="C124" t="s">
+        <v>2</v>
+      </c>
+      <c r="D124">
+        <v>19546</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>19</v>
+      </c>
+      <c r="B125" t="s">
+        <v>20</v>
+      </c>
+      <c r="C125" t="s">
+        <v>2</v>
+      </c>
+      <c r="D125">
+        <v>20524</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>19</v>
+      </c>
+      <c r="B126" t="s">
+        <v>20</v>
+      </c>
+      <c r="C126" t="s">
+        <v>2</v>
+      </c>
+      <c r="D126">
+        <v>21744</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>19</v>
+      </c>
+      <c r="B127" t="s">
+        <v>20</v>
+      </c>
+      <c r="C127" t="s">
+        <v>2</v>
+      </c>
+      <c r="D127">
+        <v>23259</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>19</v>
+      </c>
+      <c r="B128" t="s">
+        <v>20</v>
+      </c>
+      <c r="C128" t="s">
+        <v>2</v>
+      </c>
+      <c r="D128">
+        <v>24046</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>19</v>
+      </c>
+      <c r="B129" t="s">
+        <v>20</v>
+      </c>
+      <c r="C129" t="s">
+        <v>2</v>
+      </c>
+      <c r="D129">
+        <v>24477</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>19</v>
+      </c>
+      <c r="B130" t="s">
+        <v>20</v>
+      </c>
+      <c r="C130" t="s">
+        <v>2</v>
+      </c>
+      <c r="D130">
+        <v>24666</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>19</v>
+      </c>
+      <c r="B131" t="s">
+        <v>20</v>
+      </c>
+      <c r="C131" t="s">
+        <v>2</v>
+      </c>
+      <c r="D131">
+        <v>24702</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>19</v>
+      </c>
+      <c r="B132" t="s">
+        <v>20</v>
+      </c>
+      <c r="C132" t="s">
+        <v>2</v>
+      </c>
+      <c r="D132">
+        <v>24915</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>19</v>
+      </c>
+      <c r="B133" t="s">
+        <v>20</v>
+      </c>
+      <c r="C133" t="s">
+        <v>2</v>
+      </c>
+      <c r="D133">
+        <v>25478</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>19</v>
+      </c>
+      <c r="B134" t="s">
+        <v>20</v>
+      </c>
+      <c r="C134" t="s">
+        <v>2</v>
+      </c>
+      <c r="D134">
+        <v>25588</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>19</v>
+      </c>
+      <c r="B135" t="s">
+        <v>20</v>
+      </c>
+      <c r="C135" t="s">
+        <v>2</v>
+      </c>
+      <c r="D135">
+        <v>25608</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>19</v>
+      </c>
+      <c r="B136" t="s">
+        <v>20</v>
+      </c>
+      <c r="C136" t="s">
+        <v>2</v>
+      </c>
+      <c r="D136">
+        <v>25647</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>19</v>
+      </c>
+      <c r="B137" t="s">
+        <v>20</v>
+      </c>
+      <c r="C137" t="s">
+        <v>2</v>
+      </c>
+      <c r="D137">
+        <v>25934</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
